--- a/diseases/d127/2005-2009.xlsx
+++ b/diseases/d127/2005-2009.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,46 +716,48 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2008-07-01</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2008-07</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2005-01</t>
+        </is>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -618,52 +765,93 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -690,46 +878,48 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2008-08-01</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2008-08</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2005-01</t>
+        </is>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -737,52 +927,165 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>SRC_IS_DOH_HISTORY</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Blæðandi veiruhitasóttir</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -809,46 +1112,48 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2008-09-01</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2008-09</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2006-01</t>
+        </is>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -856,52 +1161,93 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -928,46 +1274,48 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2008-10-01</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2008-10</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2006-01</t>
+        </is>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -975,52 +1323,165 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>SRC_IS_DOH_HISTORY</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Blæðandi veiruhitasóttir</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1047,46 +1508,48 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2008-11-01</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2008-11</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2007-01</t>
+        </is>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1094,52 +1557,93 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1166,46 +1670,48 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2008-12-01</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2008-12</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2007-01</t>
+        </is>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1213,52 +1719,165 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>SRC_IS_DOH_HISTORY</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Blæðandi veiruhitasóttir</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1285,46 +1904,48 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2008-01</t>
+        </is>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1332,52 +1953,93 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1404,46 +2066,48 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2009-02-01</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2009-02</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2008-01</t>
+        </is>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1451,52 +2115,165 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>SRC_IS_DOH_HISTORY</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Blæðandi veiruhitasóttir</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1523,46 +2300,48 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2009-03-01</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2009-03</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
+          <t>2008-07-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2008-07</t>
+        </is>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1570,50 +2349,77 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1642,46 +2448,48 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2009-04-01</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2009-04</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
+          <t>2008-08-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2008-08</t>
+        </is>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1689,50 +2497,77 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1761,46 +2596,48 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2009-05-01</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2009-05</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2008-09</t>
+        </is>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1808,50 +2645,77 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1880,46 +2744,48 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2009-06-01</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2009-06</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
+          <t>2008-10-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2008-10</t>
+        </is>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1927,50 +2793,77 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="BA13" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="BB13" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1999,46 +2892,48 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2009-07-01</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2009-07</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
+          <t>2008-11-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2008-11</t>
+        </is>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2046,50 +2941,77 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="BA14" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="BB14" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2118,46 +3040,48 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2009-08-01</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2009-08</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
+          <t>2008-12-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2008-12</t>
+        </is>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2165,50 +3089,77 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="BA15" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="BB15" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2237,46 +3188,48 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2009-09-01</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2284,50 +3237,77 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="BA16" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="BB16" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2356,46 +3336,48 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2009-10-01</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2009-10</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2403,52 +3385,93 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2475,46 +3498,48 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2009-11-01</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2009-11</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2522,52 +3547,165 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>SRC_IS_DOH_HISTORY</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Blæðandi veiruhitasóttir</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2594,97 +3732,1606 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2009-02-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2009-02</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2009-03</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2009-04-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2009-04</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2009-05-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2009-05</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2009-06</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2009-07-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>2009-12-01</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>2009-12</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="AW29" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AY29" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="BA29" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="BB29" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="BC29" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2735,7 +5382,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
     </row>
@@ -2802,62 +5449,104 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2009-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2009-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2005-01-01</t>
         </is>

--- a/diseases/d127/2005-2009.xlsx
+++ b/diseases/d127/2005-2009.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -3383,9 +3371,6 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">

--- a/diseases/d127/2005-2009.xlsx
+++ b/diseases/d127/2005-2009.xlsx
@@ -1900,12 +1900,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -1992,42 +1992,42 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2105,22 +2105,22 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Blæðandi veiruhitasóttir</t>
+          <t>Other Viral Haemorrhagic fevers</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT9" t="n">
@@ -2226,42 +2226,42 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2337,9 +2337,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2348,68 +2345,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2447,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2471,12 +2482,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2485,79 +2496,165 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2716,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2767,12 +2864,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2915,12 +3012,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3063,12 +3160,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3211,12 +3308,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3329,12 +3426,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3359,12 +3456,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3373,6 +3470,9 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3381,82 +3481,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3483,17 +3569,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3532,34 +3618,17 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3567,64 +3636,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN18" t="b">
-        <v>1</v>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3642,7 +3653,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -3655,42 +3666,42 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3717,17 +3728,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3752,12 +3763,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3766,79 +3777,165 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3997,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -4018,12 +4115,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4048,12 +4145,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4062,9 +4159,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4073,68 +4167,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4161,17 +4269,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4196,12 +4304,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4210,79 +4318,165 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4538,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4492,12 +4686,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4640,12 +4834,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4788,12 +4982,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4936,12 +5130,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -5084,12 +5278,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5232,12 +5426,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5317,6 +5511,598 @@
         </is>
       </c>
       <c r="BC29" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -5438,7 +6224,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -5448,7 +6234,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -5468,7 +6254,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -5478,7 +6264,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d127/2005-2009.xlsx
+++ b/diseases/d127/2005-2009.xlsx
@@ -1114,12 +1114,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1206,42 +1206,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_PL_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Blæðandi veiruhitasóttir</t>
+          <t>Other Viral Haemorrhagic fevers</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:PL:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1440,42 +1440,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2105,17 +2105,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
+          <t>SRC_PL_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>country:FR:national</t>
+          <t>country:PL:national</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT9" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT10" t="n">
@@ -2385,42 +2385,42 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2498,22 +2498,22 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_CZ_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Blæðandi veiruhitasóttir</t>
+          <t>Other Viral Haemorrhagic fevers</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CZ:national</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>Czechia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT11" t="n">
@@ -2619,42 +2619,42 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2730,9 +2730,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2741,68 +2738,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2829,17 +2840,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2864,12 +2875,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2878,79 +2889,165 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2982,12 +3079,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3012,12 +3109,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3026,9 +3123,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3037,68 +3131,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3125,17 +3233,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3160,12 +3268,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3174,79 +3282,165 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3278,12 +3472,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3308,12 +3502,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3322,9 +3516,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3333,68 +3524,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3421,17 +3626,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3456,12 +3661,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3470,79 +3675,165 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_CZ_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:CZ:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Czechia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3865,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3604,12 +3895,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3628,7 +3919,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3653,7 +3944,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -3671,7 +3962,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -3691,7 +3982,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -3733,12 +4024,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3763,12 +4054,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3779,17 +4070,17 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
+          <t>SRC_ES_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3819,7 +4110,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>country:FR:national</t>
+          <t>country:ES:national</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3859,7 +4150,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -3887,7 +4178,7 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT19" t="n">
@@ -3905,7 +4196,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -3925,7 +4216,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -3967,12 +4258,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3997,12 +4288,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -4011,9 +4302,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4022,68 +4310,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4110,17 +4412,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4145,12 +4447,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4159,17 +4461,34 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -4177,6 +4496,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4194,7 +4571,7 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT21" t="n">
@@ -4207,42 +4584,42 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4269,17 +4646,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4304,12 +4681,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4318,34 +4695,17 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -4353,64 +4713,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN22" t="b">
-        <v>1</v>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4428,7 +4730,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT22" t="n">
@@ -4441,42 +4743,42 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4503,17 +4805,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4538,12 +4840,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4552,79 +4854,165 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_GR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:GR:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4656,12 +5044,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4686,12 +5074,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4700,9 +5088,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4711,68 +5096,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4799,17 +5198,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4834,12 +5233,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4848,79 +5247,165 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN25" t="b">
+        <v>1</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4952,12 +5437,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4982,12 +5467,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4996,9 +5481,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5007,68 +5489,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5095,17 +5591,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -5130,12 +5626,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -5144,79 +5640,165 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_IT_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:IT:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Italy annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
+        <v>1</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5248,12 +5830,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5278,12 +5860,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5292,9 +5874,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5303,68 +5882,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5391,17 +5984,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5426,12 +6019,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5440,79 +6033,165 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5544,12 +6223,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5574,12 +6253,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5588,9 +6267,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5599,68 +6275,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5687,17 +6377,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5722,12 +6412,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5736,79 +6426,165 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_RO_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:RO:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>1</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5870,12 +6646,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -6018,12 +6794,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -6103,6 +6879,5518 @@
         </is>
       </c>
       <c r="BC33" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2008-09</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2008-10-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2008-10</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2008-11-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2008-11</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2008-12-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2008-12</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_CZ_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:CZ:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Czechia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_GR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:GR:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC_IT_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>country:IT:national</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Italy annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_RO_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:RO:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2009-02-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2009-02</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2009-03</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2009-04-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2009-04</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2009-05-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2009-05</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2009-06</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2009-07-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -6224,7 +12512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -6234,7 +12522,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -6254,7 +12542,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -6264,7 +12552,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
